--- a/artfynd/A 26736-2023 artfynd.xlsx
+++ b/artfynd/A 26736-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 26736-2023 artfynd.xlsx
+++ b/artfynd/A 26736-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>110392126</v>
       </c>
       <c r="B2" t="n">
-        <v>103602</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -731,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428488.9709374183</v>
+        <v>428489</v>
       </c>
       <c r="R2" t="n">
-        <v>6169129.956830639</v>
+        <v>6169131</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,19 +759,9 @@
           <t>2023-06-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-06-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 26736-2023 artfynd.xlsx
+++ b/artfynd/A 26736-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>110392126</v>
       </c>
       <c r="B2" t="n">
-        <v>106366</v>
+        <v>106367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26736-2023 artfynd.xlsx
+++ b/artfynd/A 26736-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>110392126</v>
       </c>
       <c r="B2" t="n">
-        <v>106367</v>
+        <v>106369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26736-2023 artfynd.xlsx
+++ b/artfynd/A 26736-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>110392126</v>
       </c>
       <c r="B2" t="n">
-        <v>106369</v>
+        <v>106373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26736-2023 artfynd.xlsx
+++ b/artfynd/A 26736-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>110392126</v>
       </c>
       <c r="B2" t="n">
-        <v>106373</v>
+        <v>106386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26736-2023 artfynd.xlsx
+++ b/artfynd/A 26736-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>110392126</v>
       </c>
       <c r="B2" t="n">
-        <v>106386</v>
+        <v>106387</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26736-2023 artfynd.xlsx
+++ b/artfynd/A 26736-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>110392126</v>
       </c>
       <c r="B2" t="n">
-        <v>106387</v>
+        <v>106390</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26736-2023 artfynd.xlsx
+++ b/artfynd/A 26736-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>110392126</v>
       </c>
       <c r="B2" t="n">
-        <v>106390</v>
+        <v>106404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26736-2023 artfynd.xlsx
+++ b/artfynd/A 26736-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>110392126</v>
       </c>
       <c r="B2" t="n">
-        <v>106404</v>
+        <v>106442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26736-2023 artfynd.xlsx
+++ b/artfynd/A 26736-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>110392126</v>
       </c>
       <c r="B2" t="n">
-        <v>106442</v>
+        <v>106456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26736-2023 artfynd.xlsx
+++ b/artfynd/A 26736-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>110392126</v>
       </c>
       <c r="B2" t="n">
-        <v>106477</v>
+        <v>106478</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26736-2023 artfynd.xlsx
+++ b/artfynd/A 26736-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>110392126</v>
       </c>
       <c r="B2" t="n">
-        <v>106478</v>
+        <v>106481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26736-2023 artfynd.xlsx
+++ b/artfynd/A 26736-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>110392126</v>
       </c>
       <c r="B2" t="n">
-        <v>106481</v>
+        <v>106491</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26736-2023 artfynd.xlsx
+++ b/artfynd/A 26736-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>110392126</v>
       </c>
       <c r="B2" t="n">
-        <v>106491</v>
+        <v>106496</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26736-2023 artfynd.xlsx
+++ b/artfynd/A 26736-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>110392126</v>
       </c>
       <c r="B2" t="n">
-        <v>106496</v>
+        <v>106497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26736-2023 artfynd.xlsx
+++ b/artfynd/A 26736-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>110392126</v>
       </c>
       <c r="B2" t="n">
-        <v>106497</v>
+        <v>106498</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26736-2023 artfynd.xlsx
+++ b/artfynd/A 26736-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>110392126</v>
       </c>
       <c r="B2" t="n">
-        <v>106498</v>
+        <v>106502</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26736-2023 artfynd.xlsx
+++ b/artfynd/A 26736-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>110392126</v>
       </c>
       <c r="B2" t="n">
-        <v>106502</v>
+        <v>106507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26736-2023 artfynd.xlsx
+++ b/artfynd/A 26736-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>110392126</v>
       </c>
       <c r="B2" t="n">
-        <v>106507</v>
+        <v>106597</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26736-2023 artfynd.xlsx
+++ b/artfynd/A 26736-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>110392126</v>
       </c>
       <c r="B2" t="n">
-        <v>106597</v>
+        <v>106598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26736-2023 artfynd.xlsx
+++ b/artfynd/A 26736-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>110392126</v>
       </c>
       <c r="B2" t="n">
-        <v>106598</v>
+        <v>106599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26736-2023 artfynd.xlsx
+++ b/artfynd/A 26736-2023 artfynd.xlsx
@@ -1214,7 +1214,7 @@
         <v>133249719</v>
       </c>
       <c r="B6" t="n">
-        <v>106614</v>
+        <v>106616</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26736-2023 artfynd.xlsx
+++ b/artfynd/A 26736-2023 artfynd.xlsx
@@ -1214,7 +1214,7 @@
         <v>133249719</v>
       </c>
       <c r="B6" t="n">
-        <v>106616</v>
+        <v>106624</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26736-2023 artfynd.xlsx
+++ b/artfynd/A 26736-2023 artfynd.xlsx
@@ -1214,7 +1214,7 @@
         <v>133249719</v>
       </c>
       <c r="B6" t="n">
-        <v>106624</v>
+        <v>106652</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26736-2023 artfynd.xlsx
+++ b/artfynd/A 26736-2023 artfynd.xlsx
@@ -1214,7 +1214,7 @@
         <v>133249719</v>
       </c>
       <c r="B6" t="n">
-        <v>106652</v>
+        <v>106662</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26736-2023 artfynd.xlsx
+++ b/artfynd/A 26736-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110392126</v>
+        <v>133249672</v>
       </c>
       <c r="B2" t="n">
-        <v>106614</v>
+        <v>105087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1331</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcklungört</t>
+          <t>Månviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pulmonaria officinalis</t>
+          <t>Lunaria rediviva</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,36 +703,28 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lövestadsåsen längst i norr, Sk</t>
+          <t>Lövestd åsar, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428489</v>
+        <v>428580</v>
       </c>
       <c r="R2" t="n">
-        <v>6169131</v>
+        <v>6168425</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,17 +748,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Vid stigen</t>
+          <t>massvis</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,52 +771,42 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Bokskog</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Alex Regnér</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alex Regnér</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110392109</v>
+        <v>110392126</v>
       </c>
       <c r="B3" t="n">
-        <v>102055</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1000</v>
+        <v>1331</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Månviol</t>
+          <t>Fläcklungört</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lunaria rediviva</t>
+          <t>Pulmonaria officinalis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -844,7 +826,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -855,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428488.9709374183</v>
+        <v>428489</v>
       </c>
       <c r="R3" t="n">
-        <v>6169129.956830639</v>
+        <v>6169131</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -888,19 +870,14 @@
           <t>2023-06-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-06-27</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Vid stigen</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -933,32 +910,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110392067</v>
+        <v>133249719</v>
       </c>
       <c r="B4" t="n">
-        <v>102055</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106680</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1000</v>
+        <v>1331</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Månviol</t>
+          <t>Fläcklungört</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lunaria rediviva</t>
+          <t>Pulmonaria officinalis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -968,7 +940,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -985,17 +957,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lövestadsåsen, Sk</t>
+          <t>Lövestad åsar, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428544.9245319642</v>
+        <v>428489</v>
       </c>
       <c r="R4" t="n">
-        <v>6168957.007733295</v>
+        <v>6169130</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1019,22 +991,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,281 +1009,18 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Bokskog</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Produktionsbokskog</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alex Regnér</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alex Regnér</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>110391976</v>
-      </c>
-      <c r="B5" t="n">
-        <v>102055</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Månviol</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Lunaria rediviva</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Lövestadsåsen, Sk</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>428579.7377008169</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6168424.50418826</v>
-      </c>
-      <c r="S5" t="n">
-        <v>25</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Sjöbo</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Lövestad</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2023-06-27</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2023-06-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Massförekomst</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Ädellövskog</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Alex Regnér</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Alex Regnér</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>133249719</v>
-      </c>
-      <c r="B6" t="n">
-        <v>106662</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1331</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Fläcklungört</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Pulmonaria officinalis</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Lövestad åsar, Sk</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>428489</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6169130</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Sjöbo</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Lövestad</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Stefan Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Stefan Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
